--- a/Result/profitability/8112.xlsx
+++ b/Result/profitability/8112.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>1.25875</v>
+        <v>1.82625</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9875</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05875</v>
+        <v>1.74125</v>
       </c>
       <c r="N3" t="n">
-        <v>2.57875</v>
+        <v>2.77125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11875</v>
+        <v>1.7775</v>
       </c>
       <c r="N4" t="n">
-        <v>2.64625</v>
+        <v>2.80875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,10 +1020,10 @@
         <v>-0.21</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05875</v>
+        <v>1.70875</v>
       </c>
       <c r="N5" t="n">
-        <v>2.41875</v>
+        <v>2.53125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>0.22</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04375</v>
+        <v>1.61</v>
       </c>
       <c r="N6" t="n">
-        <v>2.3725</v>
+        <v>2.51375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>0.95375</v>
+        <v>1.22125</v>
       </c>
       <c r="N7" t="n">
-        <v>2.37375</v>
+        <v>2.27375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1395,13 +1395,13 @@
         <v>0.62</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6062500000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>2.1925</v>
+        <v>2.1825</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8112</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>150611</v>
+      </c>
+      <c r="D75" t="n">
+        <v>144931</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5680</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4830</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-945</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3885</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2895</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.94375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.20875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4168797953964194</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02077922077922079</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>15.29411764705882</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3135888501742159</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
